--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778714</v>
+        <v>127778719</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1113,23 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603815</v>
+        <v>603817</v>
       </c>
       <c r="R6" t="n">
-        <v>6693033</v>
+        <v>6693023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1162,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1197,7 @@
         <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,23 +1326,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R8" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1371,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,23 +1113,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R6" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1158,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,7 +1188,7 @@
         <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778714</v>
+        <v>127778719</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,19 +1317,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603815</v>
+        <v>603817</v>
       </c>
       <c r="R8" t="n">
-        <v>6693033</v>
+        <v>6693023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778714</v>
+        <v>127778719</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1113,23 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603815</v>
+        <v>603817</v>
       </c>
       <c r="R6" t="n">
-        <v>6693033</v>
+        <v>6693023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1162,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1197,7 @@
         <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,23 +1326,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R8" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1371,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,23 +1113,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R6" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1158,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127778715</v>
+        <v>127778719</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,19 +1215,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603737</v>
+        <v>603817</v>
       </c>
       <c r="R7" t="n">
-        <v>6693104</v>
+        <v>6693023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1264,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778714</v>
+        <v>127778715</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603815</v>
+        <v>603737</v>
       </c>
       <c r="R8" t="n">
-        <v>6693033</v>
+        <v>6693104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127778719</v>
+        <v>127778715</v>
       </c>
       <c r="B7" t="n">
         <v>98468</v>
@@ -1215,23 +1215,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603817</v>
+        <v>603737</v>
       </c>
       <c r="R7" t="n">
-        <v>6693023</v>
+        <v>6693104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,11 +1260,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778715</v>
+        <v>127778719</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1326,19 +1317,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603737</v>
+        <v>603817</v>
       </c>
       <c r="R8" t="n">
-        <v>6693104</v>
+        <v>6693023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778714</v>
+        <v>127778719</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1113,23 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603815</v>
+        <v>603817</v>
       </c>
       <c r="R6" t="n">
-        <v>6693033</v>
+        <v>6693023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1162,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1197,7 @@
         <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,23 +1326,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R8" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1371,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778719</v>
+        <v>127778714</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,23 +1113,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603817</v>
+        <v>603815</v>
       </c>
       <c r="R6" t="n">
-        <v>6693023</v>
+        <v>6693033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1158,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,7 +1188,7 @@
         <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778714</v>
+        <v>127778719</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,19 +1317,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603815</v>
+        <v>603817</v>
       </c>
       <c r="R8" t="n">
-        <v>6693033</v>
+        <v>6693023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,205 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128320596</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57666</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603745</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692978</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128334270</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6693075</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778714</v>
+        <v>127778715</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603815</v>
+        <v>603737</v>
       </c>
       <c r="R6" t="n">
-        <v>6693033</v>
+        <v>6693104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127778715</v>
+        <v>127778714</v>
       </c>
       <c r="B7" t="n">
         <v>98470</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603737</v>
+        <v>603815</v>
       </c>
       <c r="R7" t="n">
-        <v>6693104</v>
+        <v>6693033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778715</v>
+        <v>127778719</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,19 +1113,23 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603737</v>
+        <v>603817</v>
       </c>
       <c r="R6" t="n">
-        <v>6693104</v>
+        <v>6693023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,6 +1162,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1197,7 @@
         <v>127778714</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778719</v>
+        <v>127778715</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,23 +1326,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråtängarna, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603817</v>
+        <v>603737</v>
       </c>
       <c r="R8" t="n">
-        <v>6693023</v>
+        <v>6693104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1371,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 med stängel</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1401,7 @@
         <v>128320596</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57667</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127778713</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127778718</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127778712</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127778717</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127778719</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127778714</v>
+        <v>127778715</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603815</v>
+        <v>603737</v>
       </c>
       <c r="R7" t="n">
-        <v>6693033</v>
+        <v>6693104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778715</v>
+        <v>127778714</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603737</v>
+        <v>603815</v>
       </c>
       <c r="R8" t="n">
-        <v>6693104</v>
+        <v>6693033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,7 +1401,7 @@
         <v>128320596</v>
       </c>
       <c r="B9" t="n">
-        <v>57667</v>
+        <v>57679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,6 +1594,344 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128602637</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92039</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603718</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6692990</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2  på samma låga</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128320597</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91677</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6693038</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>på gammal granstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # på gammal granstubbe</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128610784</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norr om Gråtängarna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>603818</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6693033</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92039</v>
+        <v>92045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>128320596</v>
       </c>
       <c r="B9" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92045</v>
+        <v>92051</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91683</v>
+        <v>91689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92051</v>
+        <v>92053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92054</v>
+        <v>92081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>128320596</v>
       </c>
       <c r="B9" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92081</v>
+        <v>92086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92091</v>
+        <v>92095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>128320596</v>
       </c>
       <c r="B9" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128334270</v>
       </c>
       <c r="B10" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92103</v>
+        <v>92108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7362-2025 artfynd.xlsx
+++ b/artfynd/A 7362-2025 artfynd.xlsx
@@ -1600,7 +1600,7 @@
         <v>128602637</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>92116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128320597</v>
       </c>
       <c r="B12" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>128610784</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
